--- a/Bases_de_Dados/FootyStats/England Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP278"/>
+  <dimension ref="A1:BP282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ5" t="n">
         <v>1</v>
@@ -2222,7 +2222,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ10" t="n">
         <v>1.93</v>
@@ -3094,7 +3094,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ17" t="n">
         <v>0.64</v>
@@ -4402,7 +4402,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.5</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ23" t="n">
         <v>0.64</v>
@@ -6579,7 +6579,7 @@
         <v>3</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ28" t="n">
         <v>1.71</v>
@@ -7236,7 +7236,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR31" t="n">
         <v>0.6899999999999999</v>
@@ -7451,10 +7451,10 @@
         <v>1</v>
       </c>
       <c r="AP32" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR32" t="n">
         <v>1.91</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.64</v>
@@ -8762,7 +8762,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR38" t="n">
         <v>1.48</v>
@@ -8980,7 +8980,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR39" t="n">
         <v>0.97</v>
@@ -9852,7 +9852,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR43" t="n">
         <v>0.6</v>
@@ -10067,10 +10067,10 @@
         <v>3</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR44" t="n">
         <v>1.38</v>
@@ -10288,7 +10288,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR45" t="n">
         <v>1.22</v>
@@ -10721,10 +10721,10 @@
         <v>2</v>
       </c>
       <c r="AP47" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR47" t="n">
         <v>2.38</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ48" t="n">
         <v>1.29</v>
@@ -11593,7 +11593,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.71</v>
@@ -14212,7 +14212,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR63" t="n">
         <v>1.68</v>
@@ -14427,7 +14427,7 @@
         <v>1.33</v>
       </c>
       <c r="AP64" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ64" t="n">
         <v>0.79</v>
@@ -14645,7 +14645,7 @@
         <v>1.33</v>
       </c>
       <c r="AP65" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.93</v>
@@ -15084,7 +15084,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR67" t="n">
         <v>1.38</v>
@@ -15738,7 +15738,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR70" t="n">
         <v>1.55</v>
@@ -16174,7 +16174,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR72" t="n">
         <v>1.81</v>
@@ -17261,7 +17261,7 @@
         <v>1</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ77" t="n">
         <v>0.93</v>
@@ -17479,7 +17479,7 @@
         <v>2</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.93</v>
@@ -19005,7 +19005,7 @@
         <v>1</v>
       </c>
       <c r="AP85" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ85" t="n">
         <v>0.93</v>
@@ -19659,10 +19659,10 @@
         <v>1.75</v>
       </c>
       <c r="AP88" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR88" t="n">
         <v>1.86</v>
@@ -20098,7 +20098,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR90" t="n">
         <v>1.48</v>
@@ -20316,7 +20316,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR91" t="n">
         <v>1.6</v>
@@ -20531,7 +20531,7 @@
         <v>0.75</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.64</v>
@@ -20967,7 +20967,7 @@
         <v>0.25</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ94" t="n">
         <v>0.29</v>
@@ -21624,7 +21624,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR97" t="n">
         <v>1.29</v>
@@ -24894,7 +24894,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR112" t="n">
         <v>0.75</v>
@@ -25109,7 +25109,7 @@
         <v>1.4</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.79</v>
@@ -25330,7 +25330,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR114" t="n">
         <v>1.66</v>
@@ -25545,7 +25545,7 @@
         <v>0.6</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ115" t="n">
         <v>1.29</v>
@@ -25766,7 +25766,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR116" t="n">
         <v>1.39</v>
@@ -26635,10 +26635,10 @@
         <v>2.6</v>
       </c>
       <c r="AP120" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR120" t="n">
         <v>1.73</v>
@@ -26853,7 +26853,7 @@
         <v>0.8</v>
       </c>
       <c r="AP121" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ121" t="n">
         <v>1.71</v>
@@ -29251,7 +29251,7 @@
         <v>1.17</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.71</v>
@@ -29690,7 +29690,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ134" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR134" t="n">
         <v>1.58</v>
@@ -29908,7 +29908,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR135" t="n">
         <v>0.77</v>
@@ -30123,7 +30123,7 @@
         <v>0.5</v>
       </c>
       <c r="AP136" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ136" t="n">
         <v>1.29</v>
@@ -30341,7 +30341,7 @@
         <v>1.33</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.57</v>
@@ -30562,7 +30562,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR138" t="n">
         <v>1.3</v>
@@ -30998,7 +30998,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR140" t="n">
         <v>1.59</v>
@@ -31213,7 +31213,7 @@
         <v>0.83</v>
       </c>
       <c r="AP141" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ141" t="n">
         <v>0.93</v>
@@ -32088,7 +32088,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR145" t="n">
         <v>1.62</v>
@@ -32306,7 +32306,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR146" t="n">
         <v>1.57</v>
@@ -32957,7 +32957,7 @@
         <v>0.86</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.93</v>
@@ -33175,10 +33175,10 @@
         <v>1.86</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR150" t="n">
         <v>1.51</v>
@@ -34265,7 +34265,7 @@
         <v>0.14</v>
       </c>
       <c r="AP155" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ155" t="n">
         <v>0.29</v>
@@ -34704,7 +34704,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR157" t="n">
         <v>1.72</v>
@@ -35573,7 +35573,7 @@
         <v>0.71</v>
       </c>
       <c r="AP161" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ161" t="n">
         <v>1.07</v>
@@ -35794,7 +35794,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR162" t="n">
         <v>1.7</v>
@@ -36663,7 +36663,7 @@
         <v>1</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ166" t="n">
         <v>0.79</v>
@@ -37102,7 +37102,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ168" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR168" t="n">
         <v>1.57</v>
@@ -37753,10 +37753,10 @@
         <v>1</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR171" t="n">
         <v>1.51</v>
@@ -37971,7 +37971,7 @@
         <v>0.75</v>
       </c>
       <c r="AP172" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ172" t="n">
         <v>0.93</v>
@@ -38843,7 +38843,7 @@
         <v>1</v>
       </c>
       <c r="AP176" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ176" t="n">
         <v>0.93</v>
@@ -39936,7 +39936,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR181" t="n">
         <v>1.49</v>
@@ -41023,7 +41023,7 @@
         <v>1.89</v>
       </c>
       <c r="AP186" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ186" t="n">
         <v>1.57</v>
@@ -41241,7 +41241,7 @@
         <v>0.11</v>
       </c>
       <c r="AP187" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ187" t="n">
         <v>0.29</v>
@@ -42116,7 +42116,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR191" t="n">
         <v>1.35</v>
@@ -42334,7 +42334,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR192" t="n">
         <v>1.39</v>
@@ -42549,7 +42549,7 @@
         <v>0.44</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ193" t="n">
         <v>0.64</v>
@@ -43642,7 +43642,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR198" t="n">
         <v>1.66</v>
@@ -44075,7 +44075,7 @@
         <v>1.44</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ200" t="n">
         <v>1.5</v>
@@ -44296,7 +44296,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ201" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR201" t="n">
         <v>1.95</v>
@@ -44514,7 +44514,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ202" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR202" t="n">
         <v>1.22</v>
@@ -44732,7 +44732,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR203" t="n">
         <v>1.57</v>
@@ -45601,10 +45601,10 @@
         <v>1.6</v>
       </c>
       <c r="AP207" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ207" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR207" t="n">
         <v>1.41</v>
@@ -46473,7 +46473,7 @@
         <v>1.4</v>
       </c>
       <c r="AP211" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ211" t="n">
         <v>1.5</v>
@@ -46691,7 +46691,7 @@
         <v>1.7</v>
       </c>
       <c r="AP212" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ212" t="n">
         <v>1.71</v>
@@ -47566,7 +47566,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ216" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR216" t="n">
         <v>1.19</v>
@@ -48653,7 +48653,7 @@
         <v>0.7</v>
       </c>
       <c r="AP221" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ221" t="n">
         <v>1.07</v>
@@ -49089,7 +49089,7 @@
         <v>0.91</v>
       </c>
       <c r="AP223" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ223" t="n">
         <v>0.93</v>
@@ -49528,7 +49528,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ225" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR225" t="n">
         <v>1.07</v>
@@ -50182,7 +50182,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ228" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR228" t="n">
         <v>1.46</v>
@@ -50400,7 +50400,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ229" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR229" t="n">
         <v>1.37</v>
@@ -50615,7 +50615,7 @@
         <v>1.27</v>
       </c>
       <c r="AP230" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ230" t="n">
         <v>1.5</v>
@@ -51487,7 +51487,7 @@
         <v>1.55</v>
       </c>
       <c r="AP234" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ234" t="n">
         <v>1.71</v>
@@ -52141,7 +52141,7 @@
         <v>1</v>
       </c>
       <c r="AP237" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ237" t="n">
         <v>1</v>
@@ -52362,7 +52362,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ238" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR238" t="n">
         <v>1.62</v>
@@ -53234,7 +53234,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ242" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR242" t="n">
         <v>1.51</v>
@@ -53449,10 +53449,10 @@
         <v>1.58</v>
       </c>
       <c r="AP243" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ243" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR243" t="n">
         <v>1.9</v>
@@ -54103,7 +54103,7 @@
         <v>0.83</v>
       </c>
       <c r="AP246" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ246" t="n">
         <v>0.79</v>
@@ -54321,7 +54321,7 @@
         <v>1.5</v>
       </c>
       <c r="AP247" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ247" t="n">
         <v>1.71</v>
@@ -54542,7 +54542,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ248" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR248" t="n">
         <v>1.21</v>
@@ -54975,10 +54975,10 @@
         <v>1.42</v>
       </c>
       <c r="AP250" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ250" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR250" t="n">
         <v>1.67</v>
@@ -61157,6 +61157,878 @@
         <v>3.07</v>
       </c>
       <c r="BP278" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" t="n">
+        <v>8223706</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="n">
+        <v>46082.45833333334</v>
+      </c>
+      <c r="F279" t="n">
+        <v>28</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Nottingham Forest</t>
+        </is>
+      </c>
+      <c r="I279" t="n">
+        <v>2</v>
+      </c>
+      <c r="J279" t="n">
+        <v>1</v>
+      </c>
+      <c r="K279" t="n">
+        <v>3</v>
+      </c>
+      <c r="L279" t="n">
+        <v>2</v>
+      </c>
+      <c r="M279" t="n">
+        <v>1</v>
+      </c>
+      <c r="N279" t="n">
+        <v>3</v>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>['6', '15']</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="Q279" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R279" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S279" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T279" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U279" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V279" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W279" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X279" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y279" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z279" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA279" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AB279" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AC279" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD279" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE279" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF279" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG279" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH279" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AI279" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AJ279" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AK279" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL279" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM279" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN279" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO279" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP279" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ279" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR279" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS279" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AT279" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU279" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV279" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW279" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX279" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY279" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ279" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA279" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB279" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC279" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD279" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BE279" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF279" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BG279" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH279" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI279" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ279" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BK279" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BL279" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM279" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BN279" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO279" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BP279" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" t="n">
+        <v>8223799</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="n">
+        <v>46082.45833333334</v>
+      </c>
+      <c r="F280" t="n">
+        <v>28</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Fulham</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur</t>
+        </is>
+      </c>
+      <c r="I280" t="n">
+        <v>2</v>
+      </c>
+      <c r="J280" t="n">
+        <v>0</v>
+      </c>
+      <c r="K280" t="n">
+        <v>2</v>
+      </c>
+      <c r="L280" t="n">
+        <v>2</v>
+      </c>
+      <c r="M280" t="n">
+        <v>1</v>
+      </c>
+      <c r="N280" t="n">
+        <v>3</v>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>['7', '34']</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="Q280" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R280" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S280" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="T280" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U280" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="V280" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="W280" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X280" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="Y280" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z280" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA280" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AB280" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AC280" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD280" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE280" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF280" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AG280" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AH280" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI280" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ280" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AK280" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM280" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AN280" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO280" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AP280" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ280" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR280" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AS280" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AT280" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AU280" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV280" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW280" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX280" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY280" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ280" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA280" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB280" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC280" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD280" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BE280" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF280" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG280" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH280" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="BI280" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ280" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK280" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BL280" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BM280" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BN280" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BO280" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BP280" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" t="n">
+        <v>8223823</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="n">
+        <v>46082.45833333334</v>
+      </c>
+      <c r="F281" t="n">
+        <v>28</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="I281" t="n">
+        <v>0</v>
+      </c>
+      <c r="J281" t="n">
+        <v>1</v>
+      </c>
+      <c r="K281" t="n">
+        <v>1</v>
+      </c>
+      <c r="L281" t="n">
+        <v>2</v>
+      </c>
+      <c r="M281" t="n">
+        <v>1</v>
+      </c>
+      <c r="N281" t="n">
+        <v>3</v>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>['57', '65']</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="Q281" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R281" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S281" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T281" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="U281" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V281" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W281" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X281" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y281" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z281" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA281" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="AB281" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="AC281" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD281" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE281" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF281" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AG281" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AH281" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI281" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ281" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AK281" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM281" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AN281" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO281" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AP281" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ281" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR281" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS281" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT281" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AU281" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV281" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW281" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX281" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY281" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ281" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA281" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB281" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC281" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD281" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BE281" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF281" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BG281" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH281" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="BI281" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ281" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BK281" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BL281" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM281" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BN281" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO281" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BP281" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" t="n">
+        <v>8223711</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="n">
+        <v>46082.5625</v>
+      </c>
+      <c r="F282" t="n">
+        <v>28</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="I282" t="n">
+        <v>1</v>
+      </c>
+      <c r="J282" t="n">
+        <v>1</v>
+      </c>
+      <c r="K282" t="n">
+        <v>2</v>
+      </c>
+      <c r="L282" t="n">
+        <v>2</v>
+      </c>
+      <c r="M282" t="n">
+        <v>1</v>
+      </c>
+      <c r="N282" t="n">
+        <v>3</v>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>['21', '66']</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>['45+2']</t>
+        </is>
+      </c>
+      <c r="Q282" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="R282" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="S282" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="T282" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U282" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="V282" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W282" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X282" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y282" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z282" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA282" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="AB282" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="AC282" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD282" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE282" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF282" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AG282" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH282" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI282" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ282" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK282" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM282" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AN282" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AO282" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AP282" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ282" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR282" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS282" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AT282" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AU282" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV282" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW282" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX282" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY282" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ282" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA282" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB282" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC282" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD282" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BE282" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF282" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG282" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH282" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI282" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ282" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK282" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BL282" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BM282" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BN282" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO282" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP282" t="n">
         <v>1.32</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/England Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP282"/>
+  <dimension ref="A1:BP291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ3" t="n">
         <v>0.93</v>
@@ -1350,7 +1350,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>1</v>
@@ -1786,7 +1786,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.71</v>
@@ -2440,7 +2440,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.71</v>
@@ -3094,7 +3094,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.36</v>
@@ -3748,7 +3748,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ16" t="n">
         <v>0.29</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.93</v>
@@ -4835,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5053,10 +5053,10 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -5492,7 +5492,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR23" t="n">
         <v>2.22</v>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.71</v>
@@ -6146,7 +6146,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR26" t="n">
         <v>1.19</v>
@@ -6361,7 +6361,7 @@
         <v>1</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ27" t="n">
         <v>0.93</v>
@@ -6579,7 +6579,7 @@
         <v>3</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ28" t="n">
         <v>1.71</v>
@@ -6800,7 +6800,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR29" t="n">
         <v>1.52</v>
@@ -7018,7 +7018,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AR30" t="n">
         <v>2.31</v>
@@ -7233,7 +7233,7 @@
         <v>1</v>
       </c>
       <c r="AP31" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.43</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.57</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ34" t="n">
         <v>0.29</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ35" t="n">
         <v>0.93</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.64</v>
@@ -8544,7 +8544,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR37" t="n">
         <v>1.08</v>
@@ -8980,7 +8980,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR39" t="n">
         <v>0.97</v>
@@ -9198,7 +9198,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR40" t="n">
         <v>0.89</v>
@@ -9413,10 +9413,10 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR41" t="n">
         <v>1.33</v>
@@ -10067,7 +10067,7 @@
         <v>3</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.36</v>
@@ -10503,7 +10503,7 @@
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AQ46" t="n">
         <v>0.64</v>
@@ -10724,7 +10724,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR47" t="n">
         <v>2.38</v>
@@ -10939,10 +10939,10 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR48" t="n">
         <v>1.21</v>
@@ -11157,7 +11157,7 @@
         <v>1</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ49" t="n">
         <v>0.93</v>
@@ -11814,7 +11814,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR52" t="n">
         <v>0.98</v>
@@ -12247,7 +12247,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ54" t="n">
         <v>1.07</v>
@@ -12465,10 +12465,10 @@
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR55" t="n">
         <v>1.41</v>
@@ -12686,7 +12686,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR56" t="n">
         <v>1.36</v>
@@ -12904,7 +12904,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR57" t="n">
         <v>1.47</v>
@@ -13337,7 +13337,7 @@
         <v>0.5</v>
       </c>
       <c r="AP59" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ59" t="n">
         <v>1</v>
@@ -13555,10 +13555,10 @@
         <v>1.5</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AR60" t="n">
         <v>1.58</v>
@@ -13773,10 +13773,10 @@
         <v>1.5</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR61" t="n">
         <v>1.56</v>
@@ -13991,7 +13991,7 @@
         <v>0.33</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ62" t="n">
         <v>1</v>
@@ -14209,7 +14209,7 @@
         <v>2.33</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.36</v>
@@ -14430,7 +14430,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR64" t="n">
         <v>2.05</v>
@@ -14648,7 +14648,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR65" t="n">
         <v>1.75</v>
@@ -14866,7 +14866,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR66" t="n">
         <v>1.61</v>
@@ -15081,7 +15081,7 @@
         <v>0.67</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ67" t="n">
         <v>1</v>
@@ -15299,7 +15299,7 @@
         <v>1</v>
       </c>
       <c r="AP68" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AQ68" t="n">
         <v>0.93</v>
@@ -15517,10 +15517,10 @@
         <v>0</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR69" t="n">
         <v>1.12</v>
@@ -15735,7 +15735,7 @@
         <v>2.33</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.43</v>
@@ -16174,7 +16174,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR72" t="n">
         <v>1.81</v>
@@ -16825,7 +16825,7 @@
         <v>1</v>
       </c>
       <c r="AP75" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ75" t="n">
         <v>1.71</v>
@@ -17261,7 +17261,7 @@
         <v>1</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ77" t="n">
         <v>0.93</v>
@@ -17479,10 +17479,10 @@
         <v>2</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AR78" t="n">
         <v>1.25</v>
@@ -17918,7 +17918,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR80" t="n">
         <v>1.51</v>
@@ -18136,7 +18136,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR81" t="n">
         <v>1.17</v>
@@ -18351,10 +18351,10 @@
         <v>1</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR82" t="n">
         <v>1.64</v>
@@ -18572,7 +18572,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR83" t="n">
         <v>1.61</v>
@@ -18787,7 +18787,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ84" t="n">
         <v>1</v>
@@ -19226,7 +19226,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR86" t="n">
         <v>1.04</v>
@@ -19441,10 +19441,10 @@
         <v>0</v>
       </c>
       <c r="AP87" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AQ87" t="n">
         <v>0.6</v>
-      </c>
-      <c r="AQ87" t="n">
-        <v>0.64</v>
       </c>
       <c r="AR87" t="n">
         <v>1.26</v>
@@ -19877,7 +19877,7 @@
         <v>1.75</v>
       </c>
       <c r="AP89" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.71</v>
@@ -20095,7 +20095,7 @@
         <v>0.5</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ90" t="n">
         <v>1</v>
@@ -20313,7 +20313,7 @@
         <v>2.5</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.36</v>
@@ -20531,7 +20531,7 @@
         <v>0.75</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.64</v>
@@ -20752,7 +20752,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR93" t="n">
         <v>1.68</v>
@@ -20967,7 +20967,7 @@
         <v>0.25</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ94" t="n">
         <v>0.29</v>
@@ -21188,7 +21188,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AR95" t="n">
         <v>0.8100000000000001</v>
@@ -21406,7 +21406,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR96" t="n">
         <v>1.68</v>
@@ -21624,7 +21624,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR97" t="n">
         <v>1.29</v>
@@ -22275,7 +22275,7 @@
         <v>1.25</v>
       </c>
       <c r="AP100" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ100" t="n">
         <v>1.07</v>
@@ -22714,7 +22714,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR102" t="n">
         <v>1.15</v>
@@ -22932,7 +22932,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR103" t="n">
         <v>1.23</v>
@@ -23147,7 +23147,7 @@
         <v>0.2</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ104" t="n">
         <v>1</v>
@@ -23368,7 +23368,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AR105" t="n">
         <v>1.32</v>
@@ -23801,7 +23801,7 @@
         <v>1</v>
       </c>
       <c r="AP107" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ107" t="n">
         <v>1.07</v>
@@ -24673,10 +24673,10 @@
         <v>1.2</v>
       </c>
       <c r="AP111" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR111" t="n">
         <v>1.88</v>
@@ -24894,7 +24894,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR112" t="n">
         <v>0.75</v>
@@ -25109,10 +25109,10 @@
         <v>1.4</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR113" t="n">
         <v>1.32</v>
@@ -25545,10 +25545,10 @@
         <v>0.6</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR115" t="n">
         <v>1.47</v>
@@ -25763,7 +25763,7 @@
         <v>1.4</v>
       </c>
       <c r="AP116" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AQ116" t="n">
         <v>1.43</v>
@@ -25981,10 +25981,10 @@
         <v>0.8</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR117" t="n">
         <v>1.48</v>
@@ -26199,7 +26199,7 @@
         <v>1.4</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.71</v>
@@ -26417,7 +26417,7 @@
         <v>1</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ119" t="n">
         <v>1.57</v>
@@ -27289,7 +27289,7 @@
         <v>0.5</v>
       </c>
       <c r="AP123" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ123" t="n">
         <v>0.64</v>
@@ -27510,7 +27510,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR124" t="n">
         <v>1.33</v>
@@ -27725,7 +27725,7 @@
         <v>0.5</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ125" t="n">
         <v>0.93</v>
@@ -28164,7 +28164,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR127" t="n">
         <v>1.49</v>
@@ -28382,7 +28382,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR128" t="n">
         <v>1.31</v>
@@ -28815,7 +28815,7 @@
         <v>0.17</v>
       </c>
       <c r="AP130" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ130" t="n">
         <v>0.29</v>
@@ -29036,7 +29036,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AR131" t="n">
         <v>1.82</v>
@@ -29251,7 +29251,7 @@
         <v>1.17</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.71</v>
@@ -29469,7 +29469,7 @@
         <v>1.17</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ133" t="n">
         <v>1.71</v>
@@ -29687,7 +29687,7 @@
         <v>2.17</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ134" t="n">
         <v>1.36</v>
@@ -30126,7 +30126,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR136" t="n">
         <v>1.79</v>
@@ -30341,7 +30341,7 @@
         <v>1.33</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.57</v>
@@ -30559,7 +30559,7 @@
         <v>0.83</v>
       </c>
       <c r="AP138" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AQ138" t="n">
         <v>1</v>
@@ -30780,7 +30780,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ139" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR139" t="n">
         <v>1.76</v>
@@ -30995,10 +30995,10 @@
         <v>2.17</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR140" t="n">
         <v>1.59</v>
@@ -31216,7 +31216,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ141" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR141" t="n">
         <v>2.04</v>
@@ -31431,10 +31431,10 @@
         <v>2</v>
       </c>
       <c r="AP142" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AR142" t="n">
         <v>1.39</v>
@@ -31652,7 +31652,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR143" t="n">
         <v>1.23</v>
@@ -31867,10 +31867,10 @@
         <v>0.43</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ144" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR144" t="n">
         <v>1.65</v>
@@ -32085,10 +32085,10 @@
         <v>1.86</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR145" t="n">
         <v>1.62</v>
@@ -32303,7 +32303,7 @@
         <v>1.14</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ146" t="n">
         <v>1</v>
@@ -32521,10 +32521,10 @@
         <v>1.14</v>
       </c>
       <c r="AP147" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR147" t="n">
         <v>1.91</v>
@@ -32739,10 +32739,10 @@
         <v>1.29</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR148" t="n">
         <v>1.6</v>
@@ -32957,10 +32957,10 @@
         <v>0.86</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ149" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR149" t="n">
         <v>1.59</v>
@@ -33175,7 +33175,7 @@
         <v>1.86</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ150" t="n">
         <v>1.43</v>
@@ -33393,10 +33393,10 @@
         <v>1.29</v>
       </c>
       <c r="AP151" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR151" t="n">
         <v>1.19</v>
@@ -35791,10 +35791,10 @@
         <v>1.75</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR162" t="n">
         <v>1.7</v>
@@ -36009,10 +36009,10 @@
         <v>0.38</v>
       </c>
       <c r="AP163" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR163" t="n">
         <v>1.17</v>
@@ -36227,10 +36227,10 @@
         <v>0.38</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ164" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR164" t="n">
         <v>1.6</v>
@@ -36445,10 +36445,10 @@
         <v>0.88</v>
       </c>
       <c r="AP165" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR165" t="n">
         <v>1.93</v>
@@ -36663,10 +36663,10 @@
         <v>1</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ166" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR166" t="n">
         <v>1.68</v>
@@ -36884,7 +36884,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ167" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR167" t="n">
         <v>1.32</v>
@@ -37099,7 +37099,7 @@
         <v>2</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ168" t="n">
         <v>1.43</v>
@@ -37317,10 +37317,10 @@
         <v>1.75</v>
       </c>
       <c r="AP169" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AR169" t="n">
         <v>1.54</v>
@@ -37535,10 +37535,10 @@
         <v>1.5</v>
       </c>
       <c r="AP170" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR170" t="n">
         <v>1.42</v>
@@ -37753,7 +37753,7 @@
         <v>1</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ171" t="n">
         <v>1</v>
@@ -42331,7 +42331,7 @@
         <v>0.89</v>
       </c>
       <c r="AP192" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ192" t="n">
         <v>1</v>
@@ -42549,10 +42549,10 @@
         <v>0.44</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ193" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR193" t="n">
         <v>1.69</v>
@@ -42767,10 +42767,10 @@
         <v>0.78</v>
       </c>
       <c r="AP194" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AQ194" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR194" t="n">
         <v>1.15</v>
@@ -42985,10 +42985,10 @@
         <v>1.89</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ195" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AR195" t="n">
         <v>1.6</v>
@@ -43203,10 +43203,10 @@
         <v>1.33</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR196" t="n">
         <v>1.64</v>
@@ -43424,7 +43424,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ197" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR197" t="n">
         <v>1.34</v>
@@ -43639,7 +43639,7 @@
         <v>1.78</v>
       </c>
       <c r="AP198" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ198" t="n">
         <v>1.43</v>
@@ -43857,10 +43857,10 @@
         <v>0.67</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ199" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR199" t="n">
         <v>1.44</v>
@@ -44075,10 +44075,10 @@
         <v>1.44</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ200" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR200" t="n">
         <v>1.47</v>
@@ -44293,10 +44293,10 @@
         <v>1.67</v>
       </c>
       <c r="AP201" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ201" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR201" t="n">
         <v>1.95</v>
@@ -44729,7 +44729,7 @@
         <v>1.8</v>
       </c>
       <c r="AP203" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ203" t="n">
         <v>1.36</v>
@@ -45165,7 +45165,7 @@
         <v>0.2</v>
       </c>
       <c r="AP205" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ205" t="n">
         <v>0.29</v>
@@ -45383,7 +45383,7 @@
         <v>0.9</v>
       </c>
       <c r="AP206" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ206" t="n">
         <v>0.93</v>
@@ -45601,10 +45601,10 @@
         <v>1.6</v>
       </c>
       <c r="AP207" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ207" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR207" t="n">
         <v>1.41</v>
@@ -45822,7 +45822,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ208" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR208" t="n">
         <v>1.31</v>
@@ -46040,7 +46040,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ209" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR209" t="n">
         <v>1.1</v>
@@ -46255,7 +46255,7 @@
         <v>0.6</v>
       </c>
       <c r="AP210" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ210" t="n">
         <v>0.64</v>
@@ -46476,7 +46476,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ211" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR211" t="n">
         <v>1.9</v>
@@ -46912,7 +46912,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ213" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR213" t="n">
         <v>1.76</v>
@@ -47130,7 +47130,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ214" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR214" t="n">
         <v>1.85</v>
@@ -47345,7 +47345,7 @@
         <v>1.1</v>
       </c>
       <c r="AP215" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ215" t="n">
         <v>1</v>
@@ -47784,7 +47784,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ217" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR217" t="n">
         <v>1.36</v>
@@ -48002,7 +48002,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ218" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AR218" t="n">
         <v>1.7</v>
@@ -48217,7 +48217,7 @@
         <v>0.9</v>
       </c>
       <c r="AP219" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AQ219" t="n">
         <v>0.93</v>
@@ -48435,7 +48435,7 @@
         <v>1.4</v>
       </c>
       <c r="AP220" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ220" t="n">
         <v>1.71</v>
@@ -48653,7 +48653,7 @@
         <v>0.7</v>
       </c>
       <c r="AP221" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ221" t="n">
         <v>1.07</v>
@@ -48874,7 +48874,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ222" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR222" t="n">
         <v>1.24</v>
@@ -49089,7 +49089,7 @@
         <v>0.91</v>
       </c>
       <c r="AP223" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ223" t="n">
         <v>0.93</v>
@@ -49307,7 +49307,7 @@
         <v>0.27</v>
       </c>
       <c r="AP224" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ224" t="n">
         <v>0.29</v>
@@ -49743,10 +49743,10 @@
         <v>1.36</v>
       </c>
       <c r="AP226" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ226" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR226" t="n">
         <v>1.53</v>
@@ -49961,7 +49961,7 @@
         <v>1.64</v>
       </c>
       <c r="AP227" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ227" t="n">
         <v>1.57</v>
@@ -50182,7 +50182,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ228" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR228" t="n">
         <v>1.46</v>
@@ -50618,7 +50618,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ230" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR230" t="n">
         <v>1.85</v>
@@ -50833,7 +50833,7 @@
         <v>0.55</v>
       </c>
       <c r="AP231" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ231" t="n">
         <v>0.64</v>
@@ -51051,7 +51051,7 @@
         <v>0.73</v>
       </c>
       <c r="AP232" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AQ232" t="n">
         <v>1.07</v>
@@ -51269,10 +51269,10 @@
         <v>1.91</v>
       </c>
       <c r="AP233" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ233" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AR233" t="n">
         <v>1.59</v>
@@ -51487,7 +51487,7 @@
         <v>1.55</v>
       </c>
       <c r="AP234" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ234" t="n">
         <v>1.71</v>
@@ -51708,7 +51708,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ235" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR235" t="n">
         <v>1.67</v>
@@ -52577,10 +52577,10 @@
         <v>0.82</v>
       </c>
       <c r="AP239" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ239" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR239" t="n">
         <v>1.45</v>
@@ -53016,7 +53016,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ241" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR241" t="n">
         <v>1.25</v>
@@ -53231,7 +53231,7 @@
         <v>1.17</v>
       </c>
       <c r="AP242" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ242" t="n">
         <v>1</v>
@@ -53670,7 +53670,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ244" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR244" t="n">
         <v>1.07</v>
@@ -53885,7 +53885,7 @@
         <v>1.75</v>
       </c>
       <c r="AP245" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ245" t="n">
         <v>1.57</v>
@@ -54106,7 +54106,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ246" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR246" t="n">
         <v>1.83</v>
@@ -54321,7 +54321,7 @@
         <v>1.5</v>
       </c>
       <c r="AP247" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ247" t="n">
         <v>1.71</v>
@@ -54539,10 +54539,10 @@
         <v>1.58</v>
       </c>
       <c r="AP248" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AQ248" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR248" t="n">
         <v>1.21</v>
@@ -54757,10 +54757,10 @@
         <v>1</v>
       </c>
       <c r="AP249" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ249" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR249" t="n">
         <v>1.7</v>
@@ -54975,7 +54975,7 @@
         <v>1.42</v>
       </c>
       <c r="AP250" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ250" t="n">
         <v>1.43</v>
@@ -55847,7 +55847,7 @@
         <v>0.92</v>
       </c>
       <c r="AP254" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ254" t="n">
         <v>1.07</v>
@@ -56068,7 +56068,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ255" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR255" t="n">
         <v>1.26</v>
@@ -56501,7 +56501,7 @@
         <v>0.83</v>
       </c>
       <c r="AP257" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ257" t="n">
         <v>0.93</v>
@@ -56719,7 +56719,7 @@
         <v>0.92</v>
       </c>
       <c r="AP258" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ258" t="n">
         <v>1</v>
@@ -56940,7 +56940,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ259" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR259" t="n">
         <v>1.48</v>
@@ -57158,7 +57158,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ260" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR260" t="n">
         <v>1.27</v>
@@ -57376,7 +57376,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ261" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AR261" t="n">
         <v>1.37</v>
@@ -57591,10 +57591,10 @@
         <v>1.92</v>
       </c>
       <c r="AP262" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AQ262" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AR262" t="n">
         <v>1.21</v>
@@ -57809,7 +57809,7 @@
         <v>0.62</v>
       </c>
       <c r="AP263" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ263" t="n">
         <v>0.64</v>
@@ -58248,7 +58248,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ265" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR265" t="n">
         <v>1.71</v>
@@ -58681,7 +58681,7 @@
         <v>1</v>
       </c>
       <c r="AP267" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ267" t="n">
         <v>0.93</v>
@@ -58902,7 +58902,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ268" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR268" t="n">
         <v>1.72</v>
@@ -59556,7 +59556,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ271" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AR271" t="n">
         <v>1.45</v>
@@ -59771,10 +59771,10 @@
         <v>1.38</v>
       </c>
       <c r="AP272" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ272" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR272" t="n">
         <v>1.48</v>
@@ -59989,7 +59989,7 @@
         <v>1.69</v>
       </c>
       <c r="AP273" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AQ273" t="n">
         <v>1.57</v>
@@ -60207,10 +60207,10 @@
         <v>0.77</v>
       </c>
       <c r="AP274" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ274" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR274" t="n">
         <v>1.59</v>
@@ -60428,7 +60428,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ275" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR275" t="n">
         <v>1.98</v>
@@ -60643,7 +60643,7 @@
         <v>1.62</v>
       </c>
       <c r="AP276" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ276" t="n">
         <v>1.71</v>
@@ -60864,7 +60864,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ277" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR277" t="n">
         <v>1.16</v>
@@ -61079,7 +61079,7 @@
         <v>1.62</v>
       </c>
       <c r="AP278" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ278" t="n">
         <v>1.71</v>
@@ -61297,7 +61297,7 @@
         <v>1.08</v>
       </c>
       <c r="AP279" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ279" t="n">
         <v>1</v>
@@ -61515,7 +61515,7 @@
         <v>1.46</v>
       </c>
       <c r="AP280" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ280" t="n">
         <v>1.36</v>
@@ -61954,7 +61954,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ282" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR282" t="n">
         <v>1.84</v>
@@ -62030,6 +62030,1968 @@
       </c>
       <c r="BP282" t="n">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" t="n">
+        <v>8223717</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="n">
+        <v>46084.6875</v>
+      </c>
+      <c r="F283" t="n">
+        <v>29</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Burnley</t>
+        </is>
+      </c>
+      <c r="I283" t="n">
+        <v>1</v>
+      </c>
+      <c r="J283" t="n">
+        <v>0</v>
+      </c>
+      <c r="K283" t="n">
+        <v>1</v>
+      </c>
+      <c r="L283" t="n">
+        <v>2</v>
+      </c>
+      <c r="M283" t="n">
+        <v>0</v>
+      </c>
+      <c r="N283" t="n">
+        <v>2</v>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>['32', '60']</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q283" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R283" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S283" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T283" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U283" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V283" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W283" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X283" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y283" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z283" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA283" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB283" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="AC283" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD283" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE283" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF283" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AG283" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH283" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI283" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ283" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK283" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL283" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM283" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AN283" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AO283" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AP283" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ283" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AR283" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS283" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT283" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU283" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV283" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW283" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX283" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY283" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ283" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA283" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB283" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC283" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD283" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BE283" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF283" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG283" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH283" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI283" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ283" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BK283" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BL283" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BM283" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN283" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO283" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BP283" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" t="n">
+        <v>8223826</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="n">
+        <v>46084.6875</v>
+      </c>
+      <c r="F284" t="n">
+        <v>29</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Leeds United</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="I284" t="n">
+        <v>0</v>
+      </c>
+      <c r="J284" t="n">
+        <v>0</v>
+      </c>
+      <c r="K284" t="n">
+        <v>0</v>
+      </c>
+      <c r="L284" t="n">
+        <v>0</v>
+      </c>
+      <c r="M284" t="n">
+        <v>1</v>
+      </c>
+      <c r="N284" t="n">
+        <v>1</v>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="Q284" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R284" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S284" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T284" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U284" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V284" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W284" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X284" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Y284" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z284" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA284" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB284" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC284" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD284" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE284" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF284" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG284" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH284" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI284" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ284" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK284" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM284" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN284" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO284" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AP284" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ284" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR284" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS284" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT284" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU284" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV284" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW284" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX284" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY284" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ284" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA284" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB284" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC284" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD284" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BE284" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF284" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG284" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH284" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI284" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ284" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK284" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BL284" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BM284" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BN284" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO284" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP284" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" t="n">
+        <v>8223825</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="n">
+        <v>46084.6875</v>
+      </c>
+      <c r="F285" t="n">
+        <v>29</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>AFC Bournemouth</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="I285" t="n">
+        <v>0</v>
+      </c>
+      <c r="J285" t="n">
+        <v>0</v>
+      </c>
+      <c r="K285" t="n">
+        <v>0</v>
+      </c>
+      <c r="L285" t="n">
+        <v>0</v>
+      </c>
+      <c r="M285" t="n">
+        <v>0</v>
+      </c>
+      <c r="N285" t="n">
+        <v>0</v>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q285" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R285" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S285" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T285" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U285" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V285" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="W285" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X285" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y285" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z285" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA285" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB285" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC285" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD285" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE285" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF285" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG285" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH285" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI285" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ285" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK285" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM285" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN285" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO285" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AP285" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ285" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR285" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS285" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT285" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU285" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV285" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW285" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX285" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY285" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ285" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA285" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB285" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC285" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD285" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BE285" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF285" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BG285" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH285" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="BI285" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ285" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BK285" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL285" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM285" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BN285" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BO285" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BP285" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" t="n">
+        <v>8223828</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="n">
+        <v>46084.71875</v>
+      </c>
+      <c r="F286" t="n">
+        <v>29</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="I286" t="n">
+        <v>0</v>
+      </c>
+      <c r="J286" t="n">
+        <v>0</v>
+      </c>
+      <c r="K286" t="n">
+        <v>0</v>
+      </c>
+      <c r="L286" t="n">
+        <v>2</v>
+      </c>
+      <c r="M286" t="n">
+        <v>1</v>
+      </c>
+      <c r="N286" t="n">
+        <v>3</v>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>['78', '90+4']</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="Q286" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R286" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S286" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="T286" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="U286" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="V286" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W286" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X286" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y286" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z286" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="AA286" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AB286" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC286" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD286" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE286" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF286" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG286" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH286" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AI286" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ286" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK286" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM286" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN286" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AO286" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP286" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AQ286" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR286" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AS286" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AT286" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AU286" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV286" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW286" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX286" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY286" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ286" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA286" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB286" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC286" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD286" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE286" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF286" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BG286" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH286" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="BI286" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ286" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BK286" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BL286" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM286" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BN286" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO286" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BP286" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" t="n">
+        <v>8223718</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="n">
+        <v>46085.6875</v>
+      </c>
+      <c r="F287" t="n">
+        <v>29</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Fulham</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>West Ham United</t>
+        </is>
+      </c>
+      <c r="I287" t="n">
+        <v>0</v>
+      </c>
+      <c r="J287" t="n">
+        <v>0</v>
+      </c>
+      <c r="K287" t="n">
+        <v>0</v>
+      </c>
+      <c r="L287" t="n">
+        <v>0</v>
+      </c>
+      <c r="M287" t="n">
+        <v>1</v>
+      </c>
+      <c r="N287" t="n">
+        <v>1</v>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="Q287" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R287" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S287" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T287" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U287" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="V287" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="W287" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X287" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y287" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z287" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA287" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB287" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AC287" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD287" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE287" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF287" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG287" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH287" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI287" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ287" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK287" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM287" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN287" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO287" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AP287" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ287" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR287" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS287" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT287" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU287" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV287" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW287" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX287" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY287" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ287" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA287" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB287" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC287" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD287" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BE287" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF287" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BG287" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH287" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="BI287" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ287" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="BK287" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL287" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM287" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BN287" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BO287" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BP287" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" t="n">
+        <v>8223716</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="n">
+        <v>46085.6875</v>
+      </c>
+      <c r="F288" t="n">
+        <v>29</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="I288" t="n">
+        <v>1</v>
+      </c>
+      <c r="J288" t="n">
+        <v>2</v>
+      </c>
+      <c r="K288" t="n">
+        <v>3</v>
+      </c>
+      <c r="L288" t="n">
+        <v>1</v>
+      </c>
+      <c r="M288" t="n">
+        <v>4</v>
+      </c>
+      <c r="N288" t="n">
+        <v>5</v>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>['2']</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>['35', '45+6', '55', '64']</t>
+        </is>
+      </c>
+      <c r="Q288" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R288" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S288" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T288" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U288" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="V288" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="W288" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X288" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="Y288" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z288" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AA288" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB288" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC288" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD288" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE288" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF288" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AG288" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH288" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI288" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ288" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK288" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM288" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN288" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO288" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AP288" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ288" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR288" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS288" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AT288" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU288" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV288" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW288" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX288" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY288" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ288" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA288" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB288" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC288" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD288" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BE288" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF288" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BG288" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH288" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="BI288" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ288" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK288" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BL288" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BM288" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN288" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO288" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BP288" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" t="n">
+        <v>8223824</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="n">
+        <v>46085.6875</v>
+      </c>
+      <c r="F289" t="n">
+        <v>29</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="I289" t="n">
+        <v>0</v>
+      </c>
+      <c r="J289" t="n">
+        <v>1</v>
+      </c>
+      <c r="K289" t="n">
+        <v>1</v>
+      </c>
+      <c r="L289" t="n">
+        <v>0</v>
+      </c>
+      <c r="M289" t="n">
+        <v>1</v>
+      </c>
+      <c r="N289" t="n">
+        <v>1</v>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>['9']</t>
+        </is>
+      </c>
+      <c r="Q289" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="R289" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S289" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T289" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U289" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="V289" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W289" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X289" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y289" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z289" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA289" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB289" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC289" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD289" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE289" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF289" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG289" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH289" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI289" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ289" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK289" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM289" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN289" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO289" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AP289" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ289" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR289" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS289" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AT289" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AU289" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV289" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW289" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX289" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY289" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ289" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA289" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB289" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC289" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD289" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BE289" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF289" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BG289" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BH289" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI289" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ289" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BK289" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BL289" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM289" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BN289" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BO289" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BP289" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" t="n">
+        <v>8223719</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="n">
+        <v>46085.6875</v>
+      </c>
+      <c r="F290" t="n">
+        <v>29</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Nottingham Forest</t>
+        </is>
+      </c>
+      <c r="I290" t="n">
+        <v>1</v>
+      </c>
+      <c r="J290" t="n">
+        <v>0</v>
+      </c>
+      <c r="K290" t="n">
+        <v>1</v>
+      </c>
+      <c r="L290" t="n">
+        <v>2</v>
+      </c>
+      <c r="M290" t="n">
+        <v>2</v>
+      </c>
+      <c r="N290" t="n">
+        <v>4</v>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>['31', '62']</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>['56', '76']</t>
+        </is>
+      </c>
+      <c r="Q290" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R290" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S290" t="n">
+        <v>6</v>
+      </c>
+      <c r="T290" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="U290" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="V290" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W290" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X290" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y290" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z290" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA290" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB290" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AC290" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD290" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE290" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF290" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG290" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH290" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI290" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ290" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK290" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM290" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AN290" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO290" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP290" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AQ290" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR290" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AS290" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT290" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AU290" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV290" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW290" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX290" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY290" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ290" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA290" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB290" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC290" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD290" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BE290" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF290" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG290" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH290" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="BI290" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ290" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK290" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BL290" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM290" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BN290" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO290" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BP290" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" t="n">
+        <v>8223818</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="n">
+        <v>46085.71875</v>
+      </c>
+      <c r="F291" t="n">
+        <v>29</v>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Newcastle United</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="I291" t="n">
+        <v>1</v>
+      </c>
+      <c r="J291" t="n">
+        <v>1</v>
+      </c>
+      <c r="K291" t="n">
+        <v>2</v>
+      </c>
+      <c r="L291" t="n">
+        <v>2</v>
+      </c>
+      <c r="M291" t="n">
+        <v>1</v>
+      </c>
+      <c r="N291" t="n">
+        <v>3</v>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>['45+6', '90']</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>['45+9']</t>
+        </is>
+      </c>
+      <c r="Q291" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R291" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S291" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T291" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U291" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="V291" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="W291" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X291" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y291" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z291" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA291" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB291" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC291" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD291" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE291" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF291" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG291" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH291" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AI291" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ291" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AK291" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM291" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN291" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AO291" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP291" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ291" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR291" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS291" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AT291" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU291" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV291" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW291" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX291" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY291" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ291" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA291" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB291" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC291" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD291" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BE291" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF291" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BG291" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH291" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="BI291" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BJ291" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="BK291" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BL291" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BM291" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BN291" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BO291" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BP291" t="n">
+        <v>1.67</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/England Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP291"/>
+  <dimension ref="A1:BP292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.6</v>
@@ -2222,7 +2222,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ24" t="n">
         <v>1.07</v>
@@ -7236,7 +7236,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR31" t="n">
         <v>0.6899999999999999</v>
@@ -10288,7 +10288,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR45" t="n">
         <v>1.22</v>
@@ -13119,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.29</v>
@@ -15738,7 +15738,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR70" t="n">
         <v>1.55</v>
@@ -17697,7 +17697,7 @@
         <v>0.67</v>
       </c>
       <c r="AP79" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.57</v>
@@ -19662,7 +19662,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR88" t="n">
         <v>1.86</v>
@@ -21621,7 +21621,7 @@
         <v>1.75</v>
       </c>
       <c r="AP97" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.67</v>
@@ -22711,7 +22711,7 @@
         <v>1</v>
       </c>
       <c r="AP102" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.4</v>
@@ -25766,7 +25766,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR116" t="n">
         <v>1.39</v>
@@ -27943,7 +27943,7 @@
         <v>0.17</v>
       </c>
       <c r="AP126" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ126" t="n">
         <v>1</v>
@@ -29908,7 +29908,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR135" t="n">
         <v>0.77</v>
@@ -31649,7 +31649,7 @@
         <v>0.43</v>
       </c>
       <c r="AP143" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ143" t="n">
         <v>1.27</v>
@@ -33178,7 +33178,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR150" t="n">
         <v>1.51</v>
@@ -36881,7 +36881,7 @@
         <v>1.25</v>
       </c>
       <c r="AP167" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ167" t="n">
         <v>1.4</v>
@@ -37102,7 +37102,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ168" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR168" t="n">
         <v>1.57</v>
@@ -43421,7 +43421,7 @@
         <v>1</v>
       </c>
       <c r="AP197" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ197" t="n">
         <v>0.93</v>
@@ -43642,7 +43642,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR198" t="n">
         <v>1.66</v>
@@ -47566,7 +47566,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ216" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR216" t="n">
         <v>1.19</v>
@@ -47781,7 +47781,7 @@
         <v>0.7</v>
       </c>
       <c r="AP217" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ217" t="n">
         <v>1.07</v>
@@ -52362,7 +52362,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ238" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR238" t="n">
         <v>1.62</v>
@@ -52795,7 +52795,7 @@
         <v>1.55</v>
       </c>
       <c r="AP240" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ240" t="n">
         <v>1.71</v>
@@ -54978,7 +54978,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ250" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR250" t="n">
         <v>1.67</v>
@@ -55411,7 +55411,7 @@
         <v>0.83</v>
       </c>
       <c r="AP252" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ252" t="n">
         <v>0.93</v>
@@ -59553,7 +59553,7 @@
         <v>1.86</v>
       </c>
       <c r="AP271" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ271" t="n">
         <v>2</v>
@@ -61736,7 +61736,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ281" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR281" t="n">
         <v>1.95</v>
@@ -63992,6 +63992,224 @@
       </c>
       <c r="BP291" t="n">
         <v>1.67</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" t="n">
+        <v>8223827</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="n">
+        <v>46086.70833333334</v>
+      </c>
+      <c r="F292" t="n">
+        <v>29</v>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="I292" t="n">
+        <v>1</v>
+      </c>
+      <c r="J292" t="n">
+        <v>3</v>
+      </c>
+      <c r="K292" t="n">
+        <v>4</v>
+      </c>
+      <c r="L292" t="n">
+        <v>1</v>
+      </c>
+      <c r="M292" t="n">
+        <v>3</v>
+      </c>
+      <c r="N292" t="n">
+        <v>4</v>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>['34']</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>['40', '45+1', '45+7']</t>
+        </is>
+      </c>
+      <c r="Q292" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R292" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S292" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T292" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U292" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="V292" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="W292" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X292" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="Y292" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z292" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA292" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AB292" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AC292" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD292" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE292" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF292" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG292" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH292" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI292" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ292" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK292" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM292" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN292" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AO292" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AP292" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AQ292" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR292" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS292" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT292" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU292" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV292" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW292" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX292" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY292" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ292" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA292" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB292" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC292" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD292" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BE292" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF292" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BG292" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH292" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="BI292" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ292" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK292" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL292" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM292" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BN292" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BO292" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BP292" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/England Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England Premier League_20252026.xlsx
@@ -62847,13 +62847,13 @@
         <v>1</v>
       </c>
       <c r="AX286" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY286" t="n">
         <v>4</v>
       </c>
       <c r="AZ286" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA286" t="n">
         <v>2</v>
